--- a/data_extactor/batch_10_fa/batch_0100_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0100_fa.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Apple Safari | نرم‌افزار ورود داده | Eko | نرم‌افزار ایمیل | Google Docs | نرم‌افزار دستگاه کامپیوتر دستی | سیستم‌های مدیریت موجودی | نرم‌افزار ردیابی موجودی | Microsoft Access | Microsoft Dynamics GP | Microsoft Edge | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Windows | Microsoft Word | Mozilla Firefox | Oracle JD Edwards EnterpriseOne | نرم‌افزار سفارش‌دهی | نرم‌افزار SAP | نرم‌افزار انتخاب صوتی | سیستم مدیریت انبار WMS | نرم‌افزار برنامه‌ریزی کاری</t>
+          <t>Apple Safari | نرم‌افزار ورود داده | Eko | نرم‌افزار ایمیل | Google Docs | نرم‌افزار دستگاه‌های کامپیوتر جیبی | سیستم‌های مدیریت موجودی | نرم‌افزار ردیابی موجودی | Microsoft Access | Microsoft Dynamics GP | Microsoft Edge | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Windows | Microsoft Word | Mozilla Firefox | Oracle JD Edwards EnterpriseOne | نرم‌افزار سفارش‌دهی | نرم‌افزار SAP | نرم‌افزار انتخاب صوتی | سیستم مدیریت انبار WMS | نرم‌افزار زمان‌بندی کار</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -513,22 +513,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | درک شفاهی | قدرت بالاتنه | وضوح گفتار | انعطاف‌پذیری حرکتی | زبردستی دستی | بیان شفاهی | درک کتبی | هماهنگی چند عضو | ثبات دست و بازو | توجه انتخابی | ترتیب‌دهی اطلاعات | تشخیص گفتار | قدرت ایستا</t>
+          <t>بینایی نزدیک | درک شفاهی | قدرت تنه | وضوح گفتار | انعطاف‌پذیری دامنه حرکت | مهارت دستی | بیان شفاهی | درک کتبی | هماهنگی چند عضو | ثبات دست و بازو | توجه انتخابی | ترتیب‌دهی اطلاعات | تشخیص گفتار | قدرت ایستا</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | داخل ساختمان، محیط کنترل‌شده | کار با یا مشارکت در یک گروه کاری یا تیم | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | اهمیت دقیق یا منظم بودن | صرف زمان به صورت ایستاده | مکالمات تلفنی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت تکرار وظایف مشابه</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا درست بودن | صرف زمان برای ایستادن | مکالمات تلفنی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>صندوق‌داران | کارمندان باجه و اجاره | کارمندان بایگانی | سرپرستان خط اول کمک‌یاران، کارگران و جابجا‌کنندگان دستی مواد | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول کارکنان فروش خرده‌فروشی | کارگران و جابجا‌کنندگان دستی بار، انبار و مواد | تحلیل‌گران لجستیک | کارمندان پست و اپراتورهای ماشین‌های پست، به جز خدمات پستی | کارمندان دفتر، عمومی | کارمندان سفارشات | بسته‌بندها و بسته‌بندی‌کنندگان دستی | کارمندان خدمات پستی | مرتب‌کنندگان، پردازش‌کنندگان و اپراتورهای ماشین‌های پردازش پست خدمات پستی | کارمندان تدارکات | کارمندان تولید، برنامه‌ریزی و تسریع | کارگران بازیافت و احیا | فروشندگان خرده‌فروشی | کارمندان ارسال، دریافت و موجودی | توزین‌کنندگان، اندازه‌گیران، بازبین‌ها و نمونه‌برداران، ثبت اسناد</t>
+          <t>صندوق‌داران | کارمندان باجه و اجاره | کارمندان بایگانی | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان رده اول کارکنان فروش خرده‌فروشی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | تحلیلگران لجستیک | کارمندان پست و اپراتورهای ماشین‌های پست، به جز اداره پست | کارمندان دفتری عمومی | کارمندان ثبت سفارش | بسته‌بندهای دستی | کارمندان خدمات پستی | دسته‌بندی‌کنندگان، پردازش‌کنندگان و اپراتورهای ماشین‌های پردازش خدمات پستی | کارمندان تدارکات | کارمندان تولید، برنامه‌ریزی و هماهنگی | کارگران بازیافت و احیا | فروشندگان خرده‌فروشی | کارمندان ارسال، دریافت و موجودی کالا | توزین‌کنندگان، اندازه‌گیران، کنترل‌کنندگان و نمونه‌برداران، ثبت اسناد</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | مانیتورینگ | درک مطلب | گوش دادن فعال | نگارش | سخن گفتن</t>
+          <t>تفکر انتقادی | نظارت | درک مطلب | گوش دادن فعال | نگارش | سخن گفتن</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مکانیکی | ایمنی و امنیت عمومی | اداره و مدیریت | شیمی | زبان انگلیسی | آموزش و پرورش | ریاضیات | کامپیوتر و الکترونیک | فیزیک | مهندسی و فناوری | خدمات مشتریان و شخصی</t>
+          <t>تولید و فرآوری | مکانیک | ایمنی و امنیت عمومی | مدیریت و اداره | شیمی | زبان انگلیسی | آموزش و پرورش | ریاضیات | رایانه و الکترونیک | فیزیک | مهندسی و فناوری | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | زبردستی دستی | زبردستی انگشتان | حساسیت به مشکل | بینایی نزدیک | هماهنگی چند عضو | دقت کنترل | سرعت ادراکی | زمان عکس‌العمل | ترتیب‌دهی اطلاعات | بینایی دور | توجه انتخابی | انعطاف‌پذیری بستار | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک کتبی | درک شفاهی | وضوح گفتار | توجه شنیداری | کنترل نرخ | بیان کتبی | اشتراک زمانی | انعطاف‌پذیری دسته‌بندی</t>
+          <t>ثبات دست و بازو | مهارت دستی | مهارت انگشتان | حساسیت به مسئله | بینایی نزدیک | هماهنگی چند عضو | دقت کنترل | سرعت ادراکی | زمان عکس‌العمل | ترتیب‌دهی اطلاعات | بینایی دور | توجه انتخابی | انعطاف‌پذیری بستار | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک کتبی | درک شفاهی | وضوح گفتار | توجه شنیداری | کنترل نرخ | بیان کتبی | تقسیم توجه | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | ایمیل | سلامت و ایمنی سایر کارگران | مکالمات تلفنی | در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | در معرض آلاینده‌ها | در معرض دماهای بسیار گرم یا سرد | کار با یا مشارکت در یک گروه کاری یا تیم | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | در معرض تجهیزات خطرناک | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | پیامد اشتباه | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | اهمیت دقیق یا منظم بودن | در معرض شرایط خطرناک | ارتباط با دیگران | فضای باز، زیر سقف | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | داخل ساختمان، محیط غیرکنترل‌شده | فشار زمانی | اهمیت تکرار وظایف مشابه | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | نزدیکی فیزیکی | پیامدهای کاری و نتایج سایر کارگران | سرعت تعیین‌شده توسط سرعت تجهیزات</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | ایمیل | سلامت و ایمنی سایر کارکنان | مکالمات تلفنی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض تجهیزات خطرناک | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | پیامد خطا | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض شرایط خطرناک | ارتباط با دیگران | فضای باز، زیر سقف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | محیط داخلی، بدون کنترل شرایط محیطی | فشار زمانی | اهمیت تکرار وظایف یکسان | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | نزدیکی فیزیکی | پیامدهای کاری و نتایج سایر کارکنان | سرعت تعیین‌شده توسط سرعت تجهیزات</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تکنسین‌های نیروگاه زیست‌توده | اپراتورها و متصدیان تجهیزات شیمیایی | اپراتورهای سیستم و کارخانه شیمیایی | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | مونتاژکنندگان موتور و سایر ماشین‌آلات | اپراتورها و متصدیان کوره، کوره پخت، اجاق، خشک‌کن و دیگ | اپراتورهای کارخانه گاز | تکنسین‌های زمین‌گرمایی | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی فلز و پلاستیک | تکنسین‌های نیروگاه برق‌آبی | مکانیک‌های ماشین‌آلات صنعتی | کارگران نگهداری ماشین‌آلات | اپراتورها و متصدیان کوره تصفیه فلز | اپراتورهای سیستم پمپ نفت، اپراتورهای پالایشگاه و سنجش‌گران | اپراتورهای نیروگاه | اپراتورهای پمپ، به جز پمپ‌کنندگان سرچاهی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جداسازی، فیلتر کردن، شفاف‌سازی، رسوب‌دهی و تقطیر | مهندسان تاسیسات و اپراتورهای دیگ بخار | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب | پمپ‌کنندگان سرچاهی</t>
+          <t>تکنسین‌های نیروگاه زیست‌توده | متصدیان و اپراتورهای تجهیزات شیمیایی | اپراتورهای کارخانه و سامانه‌های شیمیایی | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | اپراتورها و متصدیان کوره، کوره پخت، فر، خشک‌کن و دیگ بخار | اپراتورهای واحدهای گاز | تکنسین‌های زمین‌گرمایی | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی، فلز و پلاستیک | تکنسین‌های نیروگاه برق‌آبی | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورها و متصدیان کوره تصفیه فلز | اپراتورهای سامانه پمپ نفت، اپراتورهای پالایشگاه و متصدیان اندازه‌گیری | اپراتورهای نیروگاه برق | اپراتورهای پمپ، به جز پمپ‌کنندگان سرچاهی | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | مهندسان تاسیسات و اپراتورهای دیگ بخار | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب | پمپ‌کنندگان سرچاهی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>مانیتورینگ | درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی</t>
+          <t>نظارت | درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | زبان انگلیسی | مکانیکی | ریاضیات</t>
+          <t>تولید و فرآوری | زبان انگلیسی | مکانیک | ریاضیات</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | درک شفاهی | حساسیت به مشکل | سرعت ادراکی | بیان شفاهی | دقت کنترل | ترتیب‌دهی اطلاعات | بیان کتبی | زبردستی دستی | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری بستار | استدلال قیاسی | درک کتبی | بینایی دور | هماهنگی چند عضو | تجسم فضایی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | زبردستی انگشتان | وضوح گفتار | تشخیص گفتار | توجه شنیداری | حساسیت شنوایی | درک عمق | تشخیص رنگ بصری | انعطاف‌پذیری حرکتی | قدرت بالاتنه | قدرت ایستا | زمان عکس‌العمل | کنترل نرخ</t>
+          <t>بینایی نزدیک | درک شفاهی | حساسیت به مسئله | سرعت ادراکی | بیان شفاهی | دقت کنترل | ترتیب‌دهی اطلاعات | بیان کتبی | مهارت دستی | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری بستار | استدلال قیاسی | درک کتبی | بینایی دور | هماهنگی چند عضو | تجسم | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | مهارت انگشتان | وضوح گفتار | تشخیص گفتار | توجه شنیداری | حساسیت شنوایی | درک عمق | تشخیص رنگ بصری | انعطاف‌پذیری دامنه حرکت | قدرت تنه | قدرت ایستا | زمان عکس‌العمل | کنترل نرخ</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | در معرض آلاینده‌ها | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | فضای باز، در معرض تمام شرایط آب و هوایی | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | سلامت و ایمنی سایر کارگران | فراوانی تصمیم‌گیری | ارتباط با دیگران | در معرض تجهیزات خطرناک | در معرض دماهای بسیار گرم یا سرد | تاثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تعیین وظایف، اولویت‌ها و اهداف | اهمیت تکرار وظایف مشابه | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا منظم بودن | صرف زمان برای انجام حرکات تکراری | در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | پیامد اشتباه | در معرض شرایط خطرناک</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض آلاینده‌ها | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | فضای باز، در معرض تمام شرایط آب و هوایی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | ارتباط با دیگران | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تعیین وظایف، اولویت‌ها و اهداف | اهمیت تکرار وظایف یکسان | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | پیامد خطا | قرار گرفتن در معرض شرایط خطرناک</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>تکنسین‌های نیروگاه زیست‌توده | اپراتورها و متصدیان تجهیزات شیمیایی | اپراتورهای سیستم و کارخانه شیمیایی | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | اپراتورها و متصدیان کوره، کوره پخت، اجاق، خشک‌کن و دیگ | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | اپراتورهای کارخانه گاز | مکانیک‌های ماشین‌آلات صنعتی | کارگران نگهداری ماشین‌آلات | اپراتورها و متصدیان کوره تصفیه فلز | اپراتورهای سیستم پمپ نفت، اپراتورهای پالایشگاه و سنجش‌گران | اپراتورهای نیروگاه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جداسازی، فیلتر کردن، شفاف‌سازی، رسوب‌دهی و تقطیر | سرویس‌کاران مخزن سپتیک و تمیزکنندگان لوله فاضلاب | اپراتورهای واحد خدمات، نفت و گاز | مهندسان تاسیسات و اپراتورهای دیگ بخار | بارگیران واگن مخزنی، کامیون و کشتی | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب | پمپ‌کنندگان سرچاهی</t>
+          <t>تکنسین‌های نیروگاه زیست‌توده | متصدیان و اپراتورهای تجهیزات شیمیایی | اپراتورهای کارخانه و سامانه‌های شیمیایی | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | اپراتورها و متصدیان کوره، کوره پخت، فر، خشک‌کن و دیگ بخار | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | اپراتورهای واحدهای گاز | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورها و متصدیان کوره تصفیه فلز | اپراتورهای سامانه پمپ نفت، اپراتورهای پالایشگاه و متصدیان اندازه‌گیری | اپراتورهای نیروگاه برق | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | سرویس‌کاران سپتیک تانک و پاک‌کنندگان لوله‌های فاضلاب | اپراتورهای واحد خدمات، نفت و گاز | مهندسان تاسیسات و اپراتورهای دیگ بخار | بارگیران واگن مخزنی، کامیون و کشتی | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب | پمپ‌کنندگان سرچاهی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>مانیتورینگ | تفکر انتقادی | سخن گفتن</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مکانیکی | ریاضیات</t>
+          <t>مکانیک | ریاضیات</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مشکل | بینایی نزدیک | ترتیب‌دهی اطلاعات | دقت کنترل | هماهنگی چند عضو | زمان عکس‌العمل | قدرت ایستا | زبردستی دستی | سرعت ادراکی | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | ثبات دست و بازو | جهت‌گیری پاسخ | وضوح گفتار | تشخیص گفتار | قدرت بالاتنه</t>
+          <t>حساسیت به مسئله | بینایی نزدیک | ترتیب‌دهی اطلاعات | دقت کنترل | هماهنگی چند عضو | زمان عکس‌العمل | قدرت ایستا | مهارت دستی | سرعت ادراکی | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | ثبات دست و بازو | جهت‌گیری پاسخ | وضوح گفتار | تشخیص گفتار | قدرت تنه</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | در معرض آلاینده‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | مکالمات تلفنی | در معرض شرایط خطرناک | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | در معرض دماهای بسیار گرم یا سرد | فراوانی تصمیم‌گیری | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | ارتباط با دیگران | در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | ایمیل | در معرض تجهیزات خطرناک | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا منظم بودن | پیامد اشتباه | در معرض شرایط نوری بسیار روشن یا ناکافی | اهمیت تکرار وظایف مشابه | فشار زمانی</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض آلاینده‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | مکالمات تلفنی | قرار گرفتن در معرض شرایط خطرناک | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فراوانی تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | ارتباط با دیگران | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | ایمیل | قرار گرفتن در معرض تجهیزات خطرناک | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | پیامد خطا | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | اهمیت تکرار وظایف یکسان | فشار زمانی</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تکنسین‌های پردازش سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | اپراتورهای سیستم و کارخانه شیمیایی | اپراتورهای دکل، نفت و گاز | حفاران زمین، به جز نفت و گاز | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | اپراتورهای کارخانه گاز | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | مهندسان نفت | اپراتورهای سیستم پمپ نفت، اپراتورهای پالایشگاه و سنجش‌گران | اپراتورهای نیروگاه | اپراتورهای پمپ، به جز پمپ‌کنندگان سرچاهی | اپراتورهای مته چرخشی، نفت و گاز | کارگران ساده، نفت و گاز | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جداسازی، فیلتر کردن، شفاف‌سازی، رسوب‌دهی و تقطیر | اپراتورهای واحد خدمات، نفت و گاز | مهندسان تاسیسات و اپراتورهای دیگ بخار | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب</t>
+          <t>تکنسین‌های فرآوری سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | اپراتورهای کارخانه و سامانه‌های شیمیایی | اپراتورهای دکل، نفت و گاز | حفاران زمین، به جز نفت و گاز | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | اپراتورهای واحدهای گاز | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | مهندسان نفت | اپراتورهای سامانه پمپ نفت، اپراتورهای پالایشگاه و متصدیان اندازه‌گیری | اپراتورهای نیروگاه برق | اپراتورهای پمپ، به جز پمپ‌کنندگان سرچاهی | اپراتورهای مته چرخشی، نفت و گاز | کارگران فنی همه‌کاره نفت و گاز | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | اپراتورهای واحد خدمات، نفت و گاز | مهندسان تاسیسات و اپراتورهای دیگ بخار | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AMCS Platform | سیستم مدیریت نگهداری کامپیوتری CMMS | نرم‌افزار Dossier | نرم‌افزار مدیریت ناوگان | نرم‌افزار سیستم موقعیت‌یابی جهانی GPS | نرم‌افزار ثبت مسافت پیموده شده | نرم‌افزار حقوق و دستمزد | نرم‌افزار Routeware | تیغه شیشه‌پاک‌کن | نرم‌افزار WAM</t>
+          <t>AMCS Platform | سیستم مدیریت نگهداری کامپیوتری CMMS | نرم‌افزار Dossier | نرم‌افزار مدیریت ناوگان | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | نرم‌افزار ثبت مسافت پیموده شده | نرم‌افزار حقوق و دستمزد | نرم‌افزار Routeware | تی شیشه‌شوی | نرم‌افزار WAM</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مکانیکی</t>
+          <t>مکانیک</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>هماهنگی چند عضو | ثبات دست و بازو | قدرت ایستا | زبردستی دستی | زمان عکس‌العمل | قدرت بالاتنه | بینایی نزدیک | بینایی دور | درک شفاهی | انعطاف‌پذیری حرکتی</t>
+          <t>هماهنگی چند عضو | ثبات دست و بازو | قدرت ایستا | مهارت دستی | زمان عکس‌العمل | قدرت تنه | بینایی نزدیک | بینایی دور | درک شفاهی | انعطاف‌پذیری دامنه حرکت</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | صرف زمان برای انجام حرکات تکراری | در معرض آلاینده‌ها | در معرض دماهای بسیار گرم یا سرد | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | آزادی در تصمیم‌گیری | فشار زمانی | در معرض تجهیزات خطرناک | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | آزادی در تصمیم‌گیری | فشار زمانی | قرار گرفتن در معرض تجهیزات خطرناک | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تمیزکنندگان وسایل نقلیه و تجهیزات | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاور | اپراتورهای ماشین‌های حفاری و بارگیری و دراگ‌لاین، معدن‌کاری سطحی | کارگران حذف مواد خطرناک | رانندگان کامیون‌های سنگین و تریلی | کمک‌یاران--کارگران استخراج | کارگران نگهداری بزرگراه | اپراتورهای بالابر و وینچ | اپراتورهای تراکتور و کامیون صنعتی | کارگران و جابجا‌کنندگان دستی بار، انبار و مواد | رانندگان کامیون سبک | اپراتورهای ماشین‌های بارگیری و جابجایی، معدن‌کاری زیرزمینی | مهندسان اپراتور و سایر اپراتورهای تجهیزات ساخت‌وساز | اپراتورهای شمع‌کوب | هماهنگ‌کنندگان بازیافت | کارگران بازیافت و احیا | سرویس‌کاران مخزن سپتیک و تمیزکنندگان لوله فاضلاب | بارگیران واگن مخزنی، کامیون و کشتی | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی</t>
+          <t>تمیزکنندگان وسایل نقلیه و تجهیزات | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاور | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | کارگران حذف مواد خطرناک | رانندگان کامیون‌های سنگین و تریلی | دستیاران--کارگران استخراج | کارگران نگهداری بزرگراه‌ها | اپراتورهای بالابر و وینچ | اپراتورهای تراکتور و کامیون صنعتی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | رانندگان کامیون‌های سبک | اپراتورهای ماشین‌های بارگیری و انتقال، معدن‌کاری زیرزمینی | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای کوبنده شمع | هماهنگ‌کنندگان بازیافت | کارگران بازیافت و احیا | سرویس‌کاران سپتیک تانک و پاک‌کنندگان لوله‌های فاضلاب | بارگیران واگن مخزنی، کامیون و کشتی | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | مانیتورینگ | تفکر انتقادی | سخن گفتن | نگارش | گوش دادن فعال</t>
+          <t>درک مطلب | نظارت | تفکر انتقادی | سخن گفتن | نگارش | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | تولید و فرآوری | زبان انگلیسی | ایمنی و امنیت عمومی</t>
+          <t>حمل و نقل | تولید و فرآوری | زبان انگلیسی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>دقت کنترل | هماهنگی چند عضو | بینایی دور | کنترل نرخ | زبردستی دستی | حساسیت به مشکل | درک عمق | زمان عکس‌العمل | سرعت ادراکی | قدرت ایستا | بینایی نزدیک | ثبات دست و بازو | درک شفاهی | وضوح گفتار | تشخیص گفتار | توجه انتخابی | زبردستی انگشتان | بیان شفاهی | انعطاف‌پذیری حرکتی | استقامت | قدرت بالاتنه | تجسم فضایی | اشتراک زمانی | توجه شنیداری | حساسیت شنوایی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | بیان کتبی | درک کتبی | تعادل کلی بدن</t>
+          <t>دقت کنترل | هماهنگی چند عضو | بینایی دور | کنترل نرخ | مهارت دستی | حساسیت به مسئله | درک عمق | زمان عکس‌العمل | سرعت ادراکی | قدرت ایستا | بینایی نزدیک | ثبات دست و بازو | درک شفاهی | وضوح گفتار | تشخیص گفتار | توجه انتخابی | مهارت انگشتان | بیان شفاهی | انعطاف‌پذیری دامنه حرکت | استقامت | قدرت تنه | تجسم | تقسیم توجه | توجه شنیداری | حساسیت شنوایی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | بیان کتبی | درک کتبی | تعادل کلی بدن</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | پیامد اشتباه | در معرض آلاینده‌ها | در معرض شرایط خطرناک | کار با یا مشارکت در یک گروه کاری یا تیم | در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | سلامت و ایمنی سایر کارگران | ارتباط با دیگران | فشار زمانی | اهمیت دقیق یا منظم بودن | اهمیت تکرار وظایف مشابه | فراوانی تصمیم‌گیری | مکالمات تلفنی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در معرض دماهای بسیار گرم یا سرد | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | در معرض تجهیزات خطرناک | در معرض مکان‌های مرتفع | پوشیدن تجهیزات محافظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | تاثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | ایمیل | آزادی در تصمیم‌گیری | داخل ساختمان، محیط غیرکنترل‌شده | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای انجام حرکات تکراری | موقعیت‌های تعارض | پیامدهای کاری و نتایج سایر کارگران | در معرض شرایط نوری بسیار روشن یا ناکافی | صرف زمان به صورت ایستاده | در معرض فضای کاری تنگ، موقعیت‌های نامناسب | سرعت تعیین‌شده توسط سرعت تجهیزات</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | پیامد خطا | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض شرایط خطرناک | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | سلامت و ایمنی سایر کارکنان | ارتباط با دیگران | فشار زمانی | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف یکسان | فراوانی تصمیم‌گیری | مکالمات تلفنی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض ارتفاعات بالا | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | ایمیل | آزادی در تصمیم‌گیری | محیط داخلی، بدون کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای انجام حرکات تکراری | موقعیت‌های تعارض | پیامدهای کاری و نتایج سایر کارکنان | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | صرف زمان برای ایستادن | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | سرعت تعیین‌شده توسط سرعت تجهیزات</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | اپراتورهای سیستم و کارخانه شیمیایی | اپراتورهای ماشین‌های استخراج مداوم | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاور | اپراتورهای ماشین‌های حفاری و بارگیری و دراگ‌لاین، معدن‌کاری سطحی | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | رانندگان کامیون‌های سنگین و تریلی | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای تراکتور و کامیون صنعتی | کارگران و جابجا‌کنندگان دستی بار، انبار و مواد | اپراتورهای ماشین‌های بارگیری و جابجایی، معدن‌کاری زیرزمینی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران نگهداری ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | اپراتورهای سیستم پمپ نفت، اپراتورهای پالایشگاه و سنجش‌گران | اپراتورهای پمپ، به جز پمپ‌کنندگان سرچاهی | کارگران بازیافت و احیا | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جداسازی، فیلتر کردن، شفاف‌سازی، رسوب‌دهی و تقطیر</t>
+          <t>مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | اپراتورهای کارخانه و سامانه‌های شیمیایی | اپراتورهای ماشین استخراج مداوم | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاور | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | رانندگان کامیون‌های سنگین و تریلی | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای تراکتور و کامیون صنعتی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | اپراتورهای ماشین‌های بارگیری و انتقال، معدن‌کاری زیرزمینی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | اپراتورهای سامانه پمپ نفت، اپراتورهای پالایشگاه و متصدیان اندازه‌گیری | اپراتورهای پمپ، به جز پمپ‌کنندگان سرچاهی | کارگران بازیافت و احیا | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>نرم‌افزار مدیریت ناوگان | نرم‌افزار مدیریت حمل‌ونقل | سیستم مدیریت انبار WMS | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | سیستم‌های مدیریت موجودی | نرم‌افزار پایگاه داده | نرم‌افزار برنامه‌ریزی | نرم‌افزار مرورگر وب | Microsoft Outlook | سیستم برنامه‌ریزی منابع سازمانی ERP | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA</t>
+          <t>نرم‌افزار مدیریت ناوگان | نرم‌افزار مدیریت حمل و نقل | سیستم مدیریت انبار WMS | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | سیستم‌های مدیریت موجودی | نرم‌افزار پایگاه داده | نرم‌افزار زمان‌بندی | نرم‌افزار مرورگر وب | Microsoft Outlook | سیستم برنامه‌ریزی منابع سازمانی ERP | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | مکانیکی | ایمنی و امنیت عمومی | زبان انگلیسی | تولید و فرآوری | ریاضیات</t>
+          <t>حمل و نقل | مکانیک | ایمنی و امنیت عمومی | زبان انگلیسی | تولید و فرآوری | ریاضیات</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>زبردستی دستی | زبردستی انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت بالاتنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری حرکتی | زمان عکس‌العمل | حساسیت به مشکل | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>داخل ساختمان، محیط غیرکنترل‌شده | صرف زمان به صورت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | در معرض آلاینده‌ها | در معرض تجهیزات خطرناک | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای خم شدن یا پیچاندن بدن | نزدیکی فیزیکی | سرعت تعیین‌شده توسط سرعت تجهیزات | سلامت و ایمنی سایر کارگران | پیامد اشتباه | درجه اتوماسیون | اهمیت تکرار وظایف مشابه | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا منظم بودن | فضای باز، در معرض تمام شرایط آب و هوایی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | در معرض لرزش کل بدن</t>
+          <t>محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای خم کردن یا چرخاندن بدن | نزدیکی فیزیکی | سرعت تعیین‌شده توسط سرعت تجهیزات | سلامت و ایمنی سایر کارکنان | پیامد خطا | میزان خودکارسازی | اهمیت تکرار وظایف یکسان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | فضای باز، در معرض تمام شرایط آب و هوایی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض ارتعاش کل بدن</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>کارگران و جابجا‌کنندگان دستی بار، انبار و مواد | اپراتورهای تراکتور و کامیون صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاور | اپراتورهای بالابر و وینچ | اپراتورهای لایروب | بارگیران واگن مخزنی، کامیون و کشتی | بسته‌بندها و بسته‌بندی‌کنندگان دستی | قفسه‌چین‌ها و پرکننده‌های سفارش | جمع‌آوران زباله و مواد بازیافتی | کارگران بازیافت و احیا | تمیزکنندگان وسایل نقلیه و تجهیزات | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | اپراتورهای پمپ، به جز پمپ‌کنندگان سرچاهی | کارمندان ارسال، دریافت و موجودی | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول کمک‌یاران، کارگران و جابجا‌کنندگان دستی مواد | مدیران حمل‌ونقل، ذخیره‌سازی و توزیع | رانندگان کامیون‌های سنگین و تریلی</t>
+          <t>کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | اپراتورهای تراکتور و کامیون صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاور | اپراتورهای بالابر و وینچ | اپراتورهای لایروب | بارگیران واگن مخزنی، کامیون و کشتی | بسته‌بندهای دستی | قفسه‌چین‌ها و پرکننده‌های سفارش | جمع‌آوران زباله و مواد بازیافتی | کارگران بازیافت و احیا | تمیزکنندگان وسایل نقلیه و تجهیزات | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | اپراتورهای پمپ، به جز پمپ‌کنندگان سرچاهی | کارمندان ارسال، دریافت و موجودی کالا | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | مدیران حمل‌ونقل، انبارداری و توزیع | رانندگان کامیون‌های سنگین و تریلی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,32 +902,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>نرم‌افزار رادار | نرم‌افزار شبیه‌ساز پرواز | نرم‌افزار ناوبری | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | نرم‌افزار نقشه برداری دیجیتال | نرم‌افزار پایگاه داده ماهواره‌ای | نرم‌افزار شبیه‌سازی و مدل‌سازی | پایگاه‌های داده الکترونیکی اطلاعات هواپیما | Microsoft Excel | Microsoft Word | Microsoft PowerPoint | نرم‌افزار ایمیل | نرم‌افزار نقشه‌برداری سطح زمین | پایگاه‌های داده تصاویر ماهواره‌ای</t>
+          <t>نرم‌افزار رادار | نرم‌افزار شبیه‌سازی پرواز | نرم‌افزار ناوبری | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | نرم‌افزار نقشه‌برداری دیجیتال | نرم‌افزار پایگاه داده ماهواره‌ای | نرم‌افزار شبیه‌سازی و مدل‌سازی | پایگاه‌های داده الکترونیکی اطلاعات هواگرد | Microsoft Excel | Microsoft Word | Microsoft PowerPoint | نرم‌افزار ایمیل | نرم‌افزار نقشه‌برداری سطح زمین | پایگاه‌های داده تصاویر ماهواره‌ای</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | مانیتورینگ | درک مطلب | یادگیری فعال | نگارش | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | حمل‌ونقل | مخابرات | کامپیوتر و الکترونیک | جغرافیا | زبان انگلیسی | اداره و مدیریت | مهندسی و فناوری | آموزش و پرورش | پرسنل و منابع انسانی</t>
+          <t>ایمنی و امنیت عمومی | حمل و نقل | مخابرات | رایانه و الکترونیک | جغرافیا | زبان انگلیسی | مدیریت و اداره | مهندسی و فناوری | آموزش و پرورش | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مشکل | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روان بودن ایده‌ها | اصالت | اشتراک زمانی | تجسم فضایی | توجه شنیداری | زمان عکس‌العمل | جهت‌گیری فضایی</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | تقسیم توجه | تجسم | توجه شنیداری | زمان عکس‌العمل | جهت‌گیری فضایی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد اشتباه | اهمیت دقیق یا منظم بودن | سلامت و ایمنی سایر کارگران | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارگران | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | مکالمات تلفنی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | در معرض شرایط خطرناک | در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | صرف زمان به صورت نشسته</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد خطا | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | مکالمات تلفنی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای نشستن</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>خلبانان، کمک‌خلبانان و مهندسان پرواز خطوط هوایی | خلبانان تجاری | کنترل‌کنندگان ترافیک هوایی | متخصصان عملیات فرودگاه | مکانیک‌ها و تکنسین‌های خدمات هواپیما | تکنسین‌های اویونیک | مهندسان هوافضا | تکنسین‌ها و فناوران مهندسی و عملیات هوافضا | مدیران مدیریت بحران | مدیران حمل‌ونقل، ذخیره‌سازی و توزیع | متخصصان لجستیک | مدیران عمومی و عملیاتی | مدیران ارشد اجرایی | سرپرستان خط اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | ماموران گشت پلیس و کلانتر | نگهبانان امنیتی | غربالگران امنیت حمل‌ونقل | متخصصان آموزش و توسعه | متخصصان بهداشت و ایمنی شغلی</t>
+          <t>خلبانان، کمک‌خلبانان و مهندسان پرواز خطوط هوایی | خلبانان تجاری | کنترلرهای ترافیک هوایی | متخصصان عملیات فرودگاه | مکانیک‌ها و تکنسین‌های خدمات هواپیما | تکنسین‌های هوانوردی | مهندسان هوافضا | تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مدیران مدیریت بحران | مدیران حمل‌ونقل، انبارداری و توزیع | لجستیسین‌ها | مدیران عمومی و عملیات | مدیران ارشد اجرایی | سرپرستان خط اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | ماموران گشت پلیس و کلانتر | نگهبانان امنیتی | غربالگران امنیتی حمل و نقل | متخصصان آموزش و توسعه | متخصصان بهداشت و ایمنی شغلی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,32 +959,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>سیستم مدیریت نگهداری کامپیوتری CMMS | نرم‌افزار رادار | نرم‌افزار مدیریت نگهداری | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار شبیه‌سازی و مدل‌سازی | نرم‌افزار ناوبری | نرم‌افزار نقشه برداری دیجیتال | نرم‌افزار پایگاه داده اطلاعات مدیریت لجستیک LMI | Microsoft PowerPoint | پایگاه داده ماهواره‌ای</t>
+          <t>سیستم مدیریت نگهداری کامپیوتری CMMS | نرم‌افزار رادار | نرم‌افزار مدیریت تعمیر و نگهداری | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار شبیه‌سازی و مدل‌سازی | نرم‌افزار ناوبری | نرم‌افزار نقشه‌برداری دیجیتال | نرم‌افزار پایگاه داده اطلاعات مدیریت لجستیک LMI | Microsoft PowerPoint | نرم‌افزار پایگاه داده ماهواره‌ای</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | مانیتورینگ | درک مطلب | یادگیری فعال | نگارش | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مکانیکی | ایمنی و امنیت عمومی | مهندسی و فناوری | حمل‌ونقل | اداره و مدیریت | فیزیک | زبان انگلیسی | پرسنل و منابع انسانی | آموزش و پرورش</t>
+          <t>مکانیک | ایمنی و امنیت عمومی | مهندسی و فناوری | حمل و نقل | مدیریت و اداره | فیزیک | زبان انگلیسی | پرسنل و منابع انسانی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مشکل | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعفاف‌پذیری دسته‌بندی | روان بودن ایده‌ها | اصالت | اشتراک زمانی | تجسم فضایی | توجه شنیداری | زمان عکس‌العمل | درک عمق | دقت کنترل</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | تقسیم توجه | تجسم | توجه شنیداری | زمان عکس‌العمل | درک عمق | دقت کنترل</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد اشتباه | اهمیت دقیق یا منظم بودن | سلامت و ایمنی سایر کارگران | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارگران | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | مکالمات تلفنی | در معرض تجهیزات خطرناک | در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | فضای باز، در معرض تمام شرایط آب و هوایی | در معرض آلاینده‌ها | صرف زمان به صورت ایستاده</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد خطا | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | مکالمات تلفنی | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای ایستادن</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مکانیک‌ها و تکنسین‌های خدمات هواپیما | تکنسین‌های اویونیک | مکانیک‌های ماشین‌آلات صنعتی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط | نصابان و تعمیرکاران تجهیزات رادیویی، سلولار و دکل | دکل‌بندها | اپراتورهای جرثقیل و تاور | مهندسان اپراتور و سایر اپراتورهای تجهیزات ساخت‌وساز | مهندسان کشتی | ملوانان و روغن‌کاران دریایی | ناخداها، افسران دوم و خلبانان شناورهای آبی | متخصصان عملیات فرودگاه | متخصصان لجستیک | مدیران حمل‌ونقل، ذخیره‌سازی و توزیع | مدیران عمومی و عملیاتی | متخصصان بهداشت و ایمنی شغلی | متخصصان آموزش و توسعه | کارگران مواد منفجره، متخصصان جابجایی مهمات و انفجارگران</t>
+          <t>مکانیک‌ها و تکنسین‌های خدمات هواپیما | تکنسین‌های هوانوردی | مکانیک‌های ماشین‌آلات صنعتی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط | نصابان و تعمیرکاران تجهیزات رادیویی، سلولی و دکل | ریگرها | اپراتورهای جرثقیل و تاور | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | مهندسان کشتی | ملوانان و روغن‌کاران دریایی | ناخدایان، افسران دوم و راهنمایان شناورهای دریایی | متخصصان عملیات فرودگاه | لجستیسین‌ها | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران عمومی و عملیات | متخصصان بهداشت و ایمنی شغلی | متخصصان آموزش و توسعه | کارگران مواد منفجره، متخصصان جابجایی مهمات و آتشبارها</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>نرم‌افزار سیستم اطلاعات جغرافیایی GIS | نرم‌افزار نقشه برداری دیجیتال | نرم‌افزار نقشه‌برداری سطح زمین | نرم‌افزار نقشه‌برداری مسیر | نرم‌افزار ناوبری | نرم‌افزار شبیه‌سازی و مدل‌سازی | نرم‌افزار رادار | Microsoft Excel | Microsoft Word | Microsoft PowerPoint | نرم‌افزار ایمیل | پایگاه‌های داده تصاویر ماهواره‌ای | نرم‌افزار پایگاه داده اطلاعات مدیریت لجستیک LMI</t>
+          <t>نرم‌افزار سیستم اطلاعات جغرافیایی GIS | نرم‌افزار نقشه‌برداری دیجیتال | نرم‌افزار نقشه‌برداری سطح زمین | نرم‌افزار نقشه‌برداری مسیر | نرم‌افزار ناوبری | نرم‌افزار شبیه‌سازی و مدل‌سازی | نرم‌افزار رادار | Microsoft Excel | Microsoft Word | Microsoft PowerPoint | نرم‌افزار ایمیل | پایگاه‌های داده تصاویر ماهواره‌ای | نرم‌افزار پایگاه داده اطلاعات مدیریت لجستیک LMI</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | مانیتورینگ | درک مطلب | یادگیری فعال | نگارش | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | جغرافیا | حمل‌ونقل | مکانیکی | اداره و مدیریت | مخابرات | زبان انگلیسی | مهندسی و فناوری | پرسنل و منابع انسانی | آموزش و پرورش</t>
+          <t>ایمنی و امنیت عمومی | جغرافیا | حمل و نقل | مکانیک | مدیریت و اداره | مخابرات | زبان انگلیسی | مهندسی و فناوری | پرسنل و منابع انسانی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مشکل | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روان بودن ایده‌ها | اصالت | اشتراک زمانی | تجسم فضایی | جهت‌گیری فضایی | زمان عکس‌العمل | درک عمق | توجه شنیداری</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | تقسیم توجه | تجسم | جهت‌گیری فضایی | زمان عکس‌العمل | درک عمق | توجه شنیداری</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد اشتباه | اهمیت دقیق یا منظم بودن | سلامت و ایمنی سایر کارگران | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارگران | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | مکالمات تلفنی | در معرض شرایط خطرناک | در معرض تجهیزات خطرناک | فضای باز، در معرض تمام شرایط آب و هوایی | در معرض دماهای بسیار گرم یا سرد | در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | در معرض فضای کاری تنگ، موقعیت‌های نامناسب | در معرض لرزش کل بدن</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد خطا | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | فشار زمانی | نزدیکی فیزیکی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | مکالمات تلفنی | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض تجهیزات خطرناک | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | قرار گرفتن در معرض ارتعاش کل بدن</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ماموران گشت پلیس و کلانتر | سرپرستان خط اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان خط اول آتش‌نشانی و پیشگیری | نگهبانان امنیتی | افسران اصلاح و تربیت و زندانبانان | مدیران مدیریت بحران | غربالگران امنیت حمل‌ونقل | تکنسین‌های فوریت‌های پزشکی | مدیران عمومی و عملیاتی | متخصصان لجستیک | مدیران حمل‌ونقل، ذخیره‌سازی و توزیع | مدیران ارشد اجرایی | متخصصان آموزش و توسعه | متخصصان بهداشت و ایمنی شغلی | افسران انطباق | تکنسین‌های نقشه‌برداری و نقشه‌کشی | کارگران مواد منفجره، متخصصان جابجایی مهمات و انفجارگران | کارگران حذف مواد خطرناک</t>
+          <t>ماموران گشت پلیس و کلانتر | سرپرستان خط اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان خط اول آتش‌نشانی و پیشگیری | نگهبانان امنیتی | افسران اصلاح و تربیت و زندانبانان | مدیران مدیریت بحران | غربالگران امنیتی حمل و نقل | تکنسین‌های فوریت‌های پزشکی | مدیران عمومی و عملیات | لجستیسین‌ها | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران ارشد اجرایی | متخصصان آموزش و توسعه | متخصصان بهداشت و ایمنی شغلی | افسران انطباق | تکنسین‌های نقشه‌برداری و نقشه‌کشی | کارگران مواد منفجره، متخصصان جابجایی مهمات و آتشبارها | کارگران حذف مواد خطرناک</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0100_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0100_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب</t>
+          <t>گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | قدرت تنه | وضوح گفتار | انعطاف‌پذیری بدنی | چابکی دستی | بیان شفاهی | درک کتبی | هماهنگی چندعضو | پایداری دست و بازو | توجه انتخابی | مرتب‌سازی اطلاعات | تشخیص گفتار | قدرت ایستا</t>
+          <t>بینایی نزدیک | درک شفاهی | قدرت تنه | وضوح گفتار | انعطاف‌پذیری دامنه حرکت | مهارت دستی | بیان شفاهی | درک کتبی | هماهنگی چند عضو | ثبات دست و بازو | توجه انتخابی | ترتیب‌دهی اطلاعات | تشخیص گفتار | قدرت ایستا</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>صندوق‌داران | متصدیان پذیرش، باجه و امانت کالا | متصدیان بایگانی و بایگان‌ها | سرپرستان رده‌اول کارگران ساده، خدماتی و جابه‌جا‌کنندگان دستی کالا | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و ناوگان جابه‌جایی مواد | سرپرستان رده‌اول فروشندگان خرده‌فروشی | کارگران ساده و متصدیان دستی جابه‌جایی بار، کالا و محموله‌ها | تحلیل‌گران لجستیک | متصدیان توزیع مرسولات و اپراتورهای دستگاه‌های پستی غیردولتی | کارمندان امور اداری و دفتری عمومی | کارمندان ثبت و پردازش سفارش‌ها | کارگران بسته‌بندی دستی | کارمندان باجه و امور پستی | متصدیان تفکیک، پردازش و اپراتورهای دستگاه‌های پستی | کارمندان تدارکات و خرید | کارمندان برنامه‌ریزی، تولید و پیگیری سفارش‌ها | کارگران بازیافت و تفکیک پسماند | فروشندگان خرده‌فروشی | کارمندان انبارداری، تحویل، ارسال و کنترل موجودی کالا | متصدیان توزین، اندازه‌گیری، بازرسی و نمونه‌برداری برای ثبت سوابق</t>
+          <t>صندوق‌داران | متصدیان باجه و کرایه کالا و خدمات | متصدیان بایگانی و اسناد | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول فروشندگان خرده‌فروشی | کارگران جابه‌جایی دستی بار، کالا و مصالح | تحلیل‌گران لجستیک و فرایند توزیع | کارمندان امور مراسلات و متصدیان ماشین‌های پستی، به جز پست دولتی | متصدیان امور دفتری و امور عمومی اداری | متصدیان ثبت و پیگیری سفارش‌ها | کارگران بسته‌بندی دستی | متصدیان باجه و امور پستی | اپراتورها و متصدیان تفکیک و پردازش پستی | کارمندان تدارکات و کارپردازی | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | کارگران بازیافت و تفکیک پسماند | فروشندگان خرده‌فروشی | کارمندان انبار، ارسال و دریافت کالا | متصدیان توزین، سنجش، بازرسی و نمونه‌برداری ثبت اسناد</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,22 +560,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>نرم‌افزار کنترل‌کننده‌های منطقی قابل‌برنامه‌ریزی PLC | نرم‌افزار سیستم مدیریت رایانه‌ای نگهداری و تعمیرات CMMS | Microsoft Excel | Microsoft Office | Microsoft Outlook | Microsoft Word</t>
+          <t>سیستم مدیریت نگهداری کامپیوتری CMMS | نرم‌افزار سیستم مدیریت رایانه‌ای نگهداری و تعمیرات CMMS | نرم‌افزار Microsoft Office | Microsoft Office | Microsoft Outlook | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | درک مطلب | شنیدن فعال | نگارش | سخن گفتن</t>
+          <t>تفکر انتقادی | نظارت | درک مطلب | گوش دادن فعال | نگارش | سخن گفتن</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مکانیک | ایمنی و امنیت عمومی | مدیریت و امور اداری | شیمی | زبان انگلیسی | آموزش و تدریس | ریاضیات | رایانه و الکترونیک | فیزیک | مهندسی و فناوری | خدمات مشتریان و خدمات فردی</t>
+          <t>تولید و فرآوری | مکانیک | ایمنی و امنیت عمومی | مدیریت و اداره | شیمی | زبان انگلیسی | آموزش و پرورش | ریاضیات | رایانه و الکترونیک | فیزیک | مهندسی و فناوری | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>پایداری دست و بازو | چابکی دستی | چابکی انگشتان | حساسیت به مسئله | دید نزدیک | هماهنگی چندعضو | دقت کنترل | سرعت ادراک | زمان واکنش | مرتب‌سازی اطلاعات | دید دور | توجه انتخابی | انعطاف‌پذیری در ادراک الگوها | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک کتبی | درک شفاهی | وضوح گفتار | توجه شنیداری | کنترل نرخ سرعت | بیان کتبی | تقسیم زمان | انعطاف‌پذیری دسته‌بندی</t>
+          <t>ثبات دست و بازو | مهارت دستی | مهارت انگشتان | حساسیت به مسئله | بینایی نزدیک | هماهنگی چند عضو | دقت کنترل | سرعت ادراکی | زمان عکس‌العمل | ترتیب‌دهی اطلاعات | بینایی دور | توجه انتخابی | انعطاف‌پذیری بستار | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک کتبی | درک شفاهی | وضوح گفتار | توجه شنیداری | کنترل نرخ | بیان کتبی | تقسیم توجه | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تکنسین‌های نیروگاه‌های زیست‌توده | اپراتورها و متصدیان تجهیزات صنایع شیمیایی | اپراتورهای فرآیند و بهره‌برداری تأسیسات و سیستم‌های شیمیایی | نصابان و تعمیرکاران شیرآلات صنعتی و ابزار دقیق، به‌جز درهای اتوماتیک | مونتاژکاران موتور و تجهیزات مکانیکی | متصدیان و اپراتورهای کوره‌ها، خشک‌کن‌ها و دیگ‌های ذوب صنعتی | اپراتورهای تأسیسات پالایش و فرآورش گاز | تکنسین‌های انرژی زمین‌گرمایی | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی فلزات و پلاستیک | تکنسین‌های نیروگاه‌های برق‌آبی | مکانیک‌های ماشین‌آلات صنعتی | تعمیرکاران و تکنسین‌های نگهداری و تعمیرات ماشین‌آلات صنعتی | اپراتورها و متصدیان کوره‌های تصفیه و ذوب فلزات | اپراتورهای پمپاژ نفت، بهره‌برداری پالایشگاه و متصدیان سنجش مخازن | اپراتورهای بهره‌برداری نیروگاه برق | اپراتورهای پمپ‌های صنعتی، به‌جز پمپ‌های سرچاهی نفت و گاز | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تفکیک، تصفیه، فیلتراسیون و تقطیر | مهندسان تأسیسات و اپراتورهای بویلرها و دیگ‌های بخار | اپراتورهای تأسیسات تصفیه آب و فاضلاب صنعتی و شهری | اپراتورهای پمپ‌های سرچاهی نفت و گاز</t>
+          <t>تکنسین‌های نیروگاه زیست‌توده | اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | مونتاژکاران موتور و سایر ماشین‌آلات | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | اپراتورهای تأسیسات و پالایشگاه‌های گاز | تکنسین‌های سامانه‌های زمین‌گرمایی | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | تکنسین‌های نیروگاه برقابی | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورها و متصدیان کوره‌های تصفیه و ذوب فلزات | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | اپراتورهای نیروگاه برق | اپراتورهای پمپ، به‌جز پمپ‌های سرچاهی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب | اپراتورهای پمپ سرچاهی نفت و گاز</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,12 +617,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>سیستم مانیتورینگ و کنترل سرپرستی و گردآوری داده SCADA | نرم‌افزار سیستم مدیریت رایانه‌ای نگهداری و تعمیرات CMMS | پایگاه‌های داده عملیاتی | Microsoft Excel | Microsoft Office | Microsoft Outlook | Microsoft Word</t>
+          <t>سیستم مدیریت نگهداری کامپیوتری CMMS | نرم‌افزار سیستم مدیریت رایانه‌ای نگهداری و تعمیرات CMMS | نرم‌افزار Microsoft Office | Microsoft Excel | Microsoft Office | Microsoft Outlook | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نظارت | درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی</t>
+          <t>نظارت | درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | حساسیت به مسئله | سرعت ادراک | بیان شفاهی | دقت کنترل | مرتب‌سازی اطلاعات | بیان کتبی | چابکی دستی | پایداری دست و بازو | توجه انتخابی | انعطاف‌پذیری در ادراک الگوها | استدلال قیاسی | درک کتبی | دید دور | هماهنگی چندعضو | تجسم فضایی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | چابکی انگشتان | وضوح گفتار | تشخیص گفتار | توجه شنیداری | حساسیت شنیداری | ادراک عمق | تشخیص رنگ | انعطاف‌پذیری بدنی | قدرت تنه | قدرت ایستا | زمان واکنش | کنترل نرخ سرعت</t>
+          <t>بینایی نزدیک | درک شفاهی | حساسیت به مسئله | سرعت ادراکی | بیان شفاهی | دقت کنترل | ترتیب‌دهی اطلاعات | بیان کتبی | مهارت دستی | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری بستار | استدلال قیاسی | درک کتبی | بینایی دور | هماهنگی چند عضو | تجسم | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | مهارت انگشتان | وضوح گفتار | تشخیص گفتار | توجه شنیداری | حساسیت شنوایی | درک عمق | تشخیص رنگ بصری | انعطاف‌پذیری دامنه حرکت | قدرت تنه | قدرت ایستا | زمان عکس‌العمل | کنترل نرخ</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>تکنسین‌های نیروگاه‌های زیست‌توده | اپراتورها و متصدیان تجهیزات صنایع شیمیایی | اپراتورهای فرآیند و بهره‌برداری تأسیسات و سیستم‌های شیمیایی | اپراتورها و متصدیان تجهیزات شست‌وشو، چربی‌زدایی و اسیدشویی فلزات | نصابان و تعمیرکاران شیرآلات صنعتی و ابزار دقیق، به‌جز درهای اتوماتیک | متصدیان و اپراتورهای کوره‌ها، خشک‌کن‌ها و دیگ‌های ذوب صنعتی | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | اپراتورهای تأسیسات پالایش و فرآورش گاز | مکانیک‌های ماشین‌آلات صنعتی | تعمیرکاران و تکنسین‌های نگهداری و تعمیرات ماشین‌آلات صنعتی | اپراتورها و متصدیان کوره‌های تصفیه و ذوب فلزات | اپراتورهای پمپاژ نفت، بهره‌برداری پالایشگاه و متصدیان سنجش مخازن | اپراتورهای بهره‌برداری نیروگاه برق | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تفکیک، تصفیه، فیلتراسیون و تقطیر | متصدیان تخلیه چاه، سرویس مخازن و شست‌وشوی شبکه فاضلاب | اپراتورهای دکل‌های تعمیراتی و خدمات چاه در صنایع نفت و گاز | مهندسان تأسیسات و اپراتورهای بویلرها و دیگ‌های بخار | متصدیان بارگیری مخزن‌دار ریلی، تانکر جاده‌ای و کشتی | اپراتورهای تأسیسات تصفیه آب و فاضلاب صنعتی و شهری | اپراتورهای پمپ‌های سرچاهی نفت و گاز</t>
+          <t>تکنسین‌های نیروگاه زیست‌توده | اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و چربی‌زدایی فلزات | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | اپراتورهای تأسیسات و پالایشگاه‌های گاز | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورها و متصدیان کوره‌های تصفیه و ذوب فلزات | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | اپراتورهای نیروگاه برق | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | سرویس‌کاران مخازن سپتیک و لایروبان مجاری فاضلاب | اپراتورهای واحدهای خدمات چاه نفت و گاز | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | متصدیان بارگیری مخزن‌دار ریلی، تانکر جاده‌ای و کشتی | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب | اپراتورهای پمپ سرچاهی نفت و گاز</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دید نزدیک | مرتب‌سازی اطلاعات | دقت کنترل | هماهنگی چندعضو | زمان واکنش | قدرت ایستا | چابکی دستی | سرعت ادراک | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | پایداری دست و بازو | جهت‌یابی پاسخ | وضوح گفتار | تشخیص گفتار | قدرت تنه</t>
+          <t>حساسیت به مسئله | بینایی نزدیک | ترتیب‌دهی اطلاعات | دقت کنترل | هماهنگی چند عضو | زمان عکس‌العمل | قدرت ایستا | مهارت دستی | سرعت ادراکی | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | ثبات دست و بازو | جهت‌گیری پاسخ | وضوح گفتار | تشخیص گفتار | قدرت تنه</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تکنسین‌های فرآوری سوخت‌های زیستی | تکنسین‌های نیروگاه‌های زیست‌توده | اپراتورهای فرآیند و بهره‌برداری تأسیسات و سیستم‌های شیمیایی | متصدیان دکل‌های حفاری نفت و گاز | حفاران چاه‌های آب و زمین‌شناسی، به‌جز نفت و گاز | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | اپراتورهای تأسیسات پالایش و فرآورش گاز | مدیران تولید و بهره‌برداری تأسیسات زمین‌گرمایی | تکنسین‌های انرژی زمین‌گرمایی | تکنسین‌های نیروگاه‌های برق‌آبی | مهندسان نفت | اپراتورهای پمپاژ نفت، بهره‌برداری پالایشگاه و متصدیان سنجش مخازن | اپراتورهای بهره‌برداری نیروگاه برق | اپراتورهای پمپ‌های صنعتی، به‌جز پمپ‌های سرچاهی نفت و گاز | اپراتورهای حفاری دورانی دکل در صنایع نفت و گاز | کارگران فنی و خدماتی دکل‌های نفت و گاز (راستابوت) | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تفکیک، تصفیه، فیلتراسیون و تقطیر | اپراتورهای دکل‌های تعمیراتی و خدمات چاه در صنایع نفت و گاز | مهندسان تأسیسات و اپراتورهای بویلرها و دیگ‌های بخار | اپراتورهای تأسیسات تصفیه آب و فاضلاب صنعتی و شهری</t>
+          <t>تکنسین‌های فراوری سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | دکل‌بانان نفت و گاز | حفاران زمین، به‌جز نفت و گاز | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | اپراتورهای تأسیسات و پالایشگاه‌های گاز | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های سامانه‌های زمین‌گرمایی | تکنسین‌های نیروگاه برقابی | مهندسان نفت | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | اپراتورهای نیروگاه برق | اپراتورهای پمپ، به‌جز پمپ‌های سرچاهی | حفاران دورانی نفت و گاز | کارگران عمومی سکو و میادین نفت و گاز | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | اپراتورهای واحدهای خدمات چاه نفت و گاز | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>هماهنگی چندعضو | پایداری دست و بازو | قدرت ایستا | چابکی دستی | زمان واکنش | قدرت تنه | دید نزدیک | دید دور | درک شفاهی | انعطاف‌پذیری بدنی</t>
+          <t>هماهنگی چند عضو | ثبات دست و بازو | قدرت ایستا | مهارت دستی | زمان عکس‌العمل | قدرت تنه | بینایی نزدیک | بینایی دور | درک شفاهی | انعطاف‌پذیری دامنه حرکت</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کارگران شست‌وشو و تنظیف خودروها و تجهیزات | اپراتورها و متصدیان سیستم‌های نوار نقاله و کانوایر | اپراتورهای جرثقیل و تاورکرین | اپراتورهای ماشین‌آلات حفاری، بارگیری و دراگ‌لاین در معادن روباز | کارگران تخصصی جمع‌آوری و امحای پسماندهای خطرناک | رانندگان کامیون‌های سنگین و تریلی | کارگران ساده بخش معدن‌کاری و استخراج | کارگران نگهداری و تعمیرات راه‌ها و جاده‌ها | اپراتورهای وینچ و بالابرهای کارگاهی | اپراتورهای تراکتورها و لیفتراک‌های صنعتی | کارگران ساده و متصدیان دستی جابه‌جایی بار، کالا و محموله‌ها | رانندگان وانت‌بار و کامیونت‌های سبک | اپراتورهای ماشین‌آلات بارگیری و باربری در معادن زیرزمینی | اپراتورهای ماشین‌آلات سنگین راه‌سازی و عمرانی | اپراتورهای دستگاه‌های شمع‌کوب | کارشناسان هماهنگی بازیافت مواد | کارگران بازیافت و تفکیک پسماند | متصدیان تخلیه چاه، سرویس مخازن و شست‌وشوی شبکه فاضلاب | متصدیان بارگیری مخزن‌دار ریلی، تانکر جاده‌ای و کشتی | بازرسان وسایل نقلیه، ناوگان و تجهیزات حمل‌ونقل، به‌جز بخش هوانوردی</t>
+          <t>شست‌وشوکاران وسایل نقلیه و تجهیزات صنعتی | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاورکرین | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | کارگران امحا و پاک‌سازی مواد خطرناک | رانندگان خودروهای سنگین و کشنده‌ها | کارگران کمکی استخراج معدن | کارگران راهداری و نگهداری جاده‌ها | اپراتورهای بالابر و وینچ | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران جابه‌جایی دستی بار، کالا و مصالح | رانندگان خودروهای باربری سبک و وانت‌بارها | اپراتورهای ماشین‌های بارگیری و حمل در معادن زیرزمینی | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | اپراتورهای دستگاه شمع‌کوب | هماهنگ‌کنندگان امور بازیافت | کارگران بازیافت و تفکیک پسماند | سرویس‌کاران مخازن سپتیک و لایروبان مجاری فاضلاب | متصدیان بارگیری مخزن‌دار ریلی، تانکر جاده‌ای و کشتی | بازرسان سامانه‌ها، تجهیزات و وسایل نقلیه ترابری (به‌جز هوانوردی)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,22 +788,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>سیستم کنترل توزیع‌شده DCS | سیستم مدیریت انبار WMS | نرم‌افزار CompuWeigh GMS | سیستم‌عامل Linux | Microsoft Excel | Microsoft Office | SAP</t>
+          <t>سیستم کنترل توزیع‌شده DCS | سیستم کنترل توزیع‌شده DCS | نرم‌افزار CompuWeigh GMS | سیستم‌عامل Linux | نرم‌افزار Microsoft Office | نرم‌افزار SAP | سیستم مدیریت انبار WMS</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | نظارت | تفکر انتقادی | سخن گفتن | نگارش | شنیدن فعال</t>
+          <t>درک مطلب | نظارت | تفکر انتقادی | سخن گفتن | نگارش | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | تولید و فرآوری | زبان انگلیسی | ایمنی و امنیت عمومی</t>
+          <t>حمل و نقل | تولید و فرآوری | زبان انگلیسی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>دقت کنترل | هماهنگی چندعضو | دید دور | کنترل نرخ سرعت | چابکی دستی | حساسیت به مسئله | ادراک عمق | زمان واکنش | سرعت ادراک | قدرت ایستا | دید نزدیک | پایداری دست و بازو | درک شفاهی | وضوح گفتار | تشخیص گفتار | توجه انتخابی | چابکی انگشتان | بیان شفاهی | انعطاف‌پذیری بدنی | استقامت بدنی | قدرت تنه | تجسم فضایی | تقسیم زمان | توجه شنیداری | حساسیت شنیداری | انعطاف‌پذیری در ادراک الگوها | مرتب‌سازی اطلاعات | بیان کتبی | درک کتبی | تعادل عمومی بدن</t>
+          <t>دقت کنترل | هماهنگی چند عضو | بینایی دور | کنترل نرخ | مهارت دستی | حساسیت به مسئله | درک عمق | زمان عکس‌العمل | سرعت ادراکی | قدرت ایستا | بینایی نزدیک | ثبات دست و بازو | درک شفاهی | وضوح گفتار | تشخیص گفتار | توجه انتخابی | مهارت انگشتان | بیان شفاهی | انعطاف‌پذیری دامنه حرکت | استقامت | قدرت تنه | تجسم | تقسیم توجه | توجه شنیداری | حساسیت شنوایی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | بیان کتبی | درک کتبی | تعادل کلی بدن</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مکانیک‌های تخصصی اتوبوس، کامیون و موتورهای دیزلی | اپراتورهای فرآیند و بهره‌برداری تأسیسات و سیستم‌های شیمیایی | اپراتورهای ماشین‌های استخراج مداوم در معادن زیرزمینی | اپراتورها و متصدیان سیستم‌های نوار نقاله و کانوایر | اپراتورهای جرثقیل و تاورکرین | اپراتورهای ماشین‌آلات حفاری، بارگیری و دراگ‌لاین در معادن روباز | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | رانندگان کامیون‌های سنگین و تریلی | اپراتورهای وینچ و بالابرهای کارگاهی | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای تراکتورها و لیفتراک‌های صنعتی | کارگران ساده و متصدیان دستی جابه‌جایی بار، کالا و محموله‌ها | اپراتورهای ماشین‌آلات بارگیری و باربری در معادن زیرزمینی | متصدیان تغذیه و تخلیه ماشین‌آلات صنعتی | تعمیرکاران و تکنسین‌های نگهداری و تعمیرات ماشین‌آلات صنعتی | مکانیک‌های ماشین‌آلات سنگین و راه‌سازی، به‌جز موتور | اپراتورهای پمپاژ نفت، بهره‌برداری پالایشگاه و متصدیان سنجش مخازن | اپراتورهای پمپ‌های صنعتی، به‌جز پمپ‌های سرچاهی نفت و گاز | کارگران بازیافت و تفکیک پسماند | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تفکیک، تصفیه، فیلتراسیون و تقطیر</t>
+          <t>مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | اپراتورهای ماشین‌های استخراج پیوسته | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاورکرین | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | رانندگان خودروهای سنگین و کشنده‌ها | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران جابه‌جایی دستی بار، کالا و مصالح | اپراتورهای ماشین‌های بارگیری و حمل در معادن زیرزمینی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | مکانیک تجهیزات سنگین متحرک | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | اپراتورهای پمپ، به‌جز پمپ‌های سرچاهی | کارگران بازیافت و تفکیک پسماند | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | مکانیک | ایمنی و امنیت عمومی | زبان انگلیسی | تولید و فرآوری | ریاضیات</t>
+          <t>حمل و نقل | مکانیک | ایمنی و امنیت عمومی | زبان انگلیسی | تولید و فرآوری | ریاضیات</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | پایداری دست و بازو | هماهنگی چندعضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت بدنی | دید نزدیک | دید دور | ادراک عمق | هماهنگی کل بدن | تعادل عمومی بدن | انعطاف‌پذیری بدنی | زمان واکنش | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>کارگران ساده و متصدیان دستی جابه‌جایی بار، کالا و محموله‌ها | اپراتورهای تراکتورها و لیفتراک‌های صنعتی | متصدیان تغذیه و تخلیه ماشین‌آلات صنعتی | اپراتورها و متصدیان سیستم‌های نوار نقاله و کانوایر | اپراتورهای جرثقیل و تاورکرین | اپراتورهای وینچ و بالابرهای کارگاهی | اپراتورهای شناورهای لایروب | متصدیان بارگیری مخزن‌دار ریلی، تانکر جاده‌ای و کشتی | کارگران بسته‌بندی دستی | متصدیان چیدمان و آماده‌سازی سفارش | متصدیان و رانندگان جمع‌آوری پسماند و مواد بازیافتی | کارگران بازیافت و تفکیک پسماند | کارگران شست‌وشو و تنظیف خودروها و تجهیزات | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | اپراتورهای پمپ‌های صنعتی، به‌جز پمپ‌های سرچاهی نفت و گاز | کارمندان انبارداری، تحویل، ارسال و کنترل موجودی کالا | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و ناوگان جابه‌جایی مواد | سرپرستان رده‌اول کارگران ساده، خدماتی و جابه‌جا‌کنندگان دستی کالا | مدیران ترابری، انبارداری و توزیع | رانندگان کامیون‌های سنگین و تریلی</t>
+          <t>کارگران جابه‌جایی دستی بار، کالا و مصالح | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاورکرین | اپراتورهای بالابر و وینچ | اپراتورهای لایروب | متصدیان بارگیری مخزن‌دار ریلی، تانکر جاده‌ای و کشتی | کارگران بسته‌بندی دستی | متصدیان چیدمان و آماده‌سازی سفارش | متصدیان و رانندگان جمع‌آوری پسماند و مواد بازیافتی | کارگران بازیافت و تفکیک پسماند | شست‌وشوکاران وسایل نقلیه و تجهیزات صنعتی | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | اپراتورهای پمپ، به‌جز پمپ‌های سرچاهی | کارمندان انبار، ارسال و دریافت کالا | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | مدیران حمل‌ونقل، انبارداری و توزیع | رانندگان خودروهای سنگین و کشنده‌ها</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | حمل‌ونقل | مخابرات | رایانه و الکترونیک | جغرافیا | زبان انگلیسی | مدیریت و امور اداری | مهندسی و فناوری | آموزش و تدریس | پرسنلی و منابع انسانی</t>
+          <t>ایمنی و امنیت عمومی | حمل و نقل | مخابرات | رایانه و الکترونیک | جغرافیا | زبان انگلیسی | مدیریت و اداره | مهندسی و فناوری | آموزش و پرورش | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | وضوح گفتار | تشخیص گفتار | دید نزدیک | دید دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | ابتکار | تقسیم زمان | تجسم فضایی | توجه شنیداری | زمان واکنش | جهت‌یابی فضایی</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | تقسیم توجه | تجسم | توجه شنیداری | زمان عکس‌العمل | جهت‌گیری فضایی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>خلبانان خطوط هوایی، کمک‌خلبانان و مهندسان پرواز | خلبانان تجاری و غیرنظامی | کنترلرهای ترافیک هوایی | کارشناسان عملیات فرودگاهی | مکانیک‌ها و تکنسین‌های خدمات و تعمیرات هواپیما | تکنسین‌های اویونیک و الکترونیک هوانوردی | مهندسان هوافضا | تکنسین‌ها و کارشناسان فناوری مهندسی و عملیات هوافضا | مدیران مدیریت بحران و شرایط اضطراری | مدیران ترابری، انبارداری و توزیع | کارشناسان لجستیک و زنجیره تأمین | مدیران ارشد اجرایی و عملیاتی | مدیران عامل | سرپرستان رده‌اول مأموران پلیس و کارآگاهان | کارآگاهان و بازرسان پرونده‌های جنایی | افسران گشت پلیس و کلانتری | نگهبانان و مأموران حراست | بازرسان گیت‌های امنیتی حمل‌ونقل | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار</t>
+          <t>خلبانان خطوط هوایی، کمک‌خلبانان و مهندسان پرواز | خلبانان تجاری | کنترلرهای ترافیک هوایی | کارشناسان عملیات فرودگاهی | مکانیک و تکنسین خدمات هواپیما | تکنسین‌های اویونیک و الکترونیک پرواز | مهندسان هوافضا | کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مدیران مدیریت بحران و پدافند غیرعامل | مدیران حمل‌ونقل، انبارداری و توزیع | کارشناسان لجستیک و مدیریت زنجیره تأمین | مدیران کل و مدیران عملیات | مدیران عامل و مدیران ارشد اجرایی | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | ماموران گشت پلیس و کلانتری | نگهبانان و ماموران حراست | ماموران بازرسی و کنترل امنیتی حمل‌ونقل | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مکانیک | ایمنی و امنیت عمومی | مهندسی و فناوری | حمل‌ونقل | مدیریت و امور اداری | فیزیک | زبان انگلیسی | پرسنلی و منابع انسانی | آموزش و تدریس</t>
+          <t>مکانیک | ایمنی و امنیت عمومی | مهندسی و فناوری | حمل و نقل | مدیریت و اداره | فیزیک | زبان انگلیسی | پرسنل و منابع انسانی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | وضوح گفتار | تشخیص گفتار | دید نزدیک | دید دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | ابتکار | تقسیم زمان | تجسم فضایی | توجه شنیداری | زمان واکنش | ادراک عمق | دقت کنترل</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | تقسیم توجه | تجسم | توجه شنیداری | زمان عکس‌العمل | درک عمق | دقت کنترل</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مکانیک‌ها و تکنسین‌های خدمات و تعمیرات هواپیما | تکنسین‌های اویونیک و الکترونیک هوانوردی | مکانیک‌های ماشین‌آلات صنعتی | مکانیک‌های ماشین‌آلات سنگین و راه‌سازی، به‌جز موتور | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | نصابان و تعمیرکاران تجهیزات مخابراتی، به‌جز خطوط ارتباطی | نصابان و تعمیرکاران دکل‌ها و تجهیزات رادیویی و سلولی | ریگرها و متصدیان بستن و مهار بار و دکل | اپراتورهای جرثقیل و تاورکرین | اپراتورهای ماشین‌آلات سنگین راه‌سازی و عمرانی | مهندسان موتورخانه و فنی شناورها | ملوانان و تکنسین‌های فنی و روغن‌کاری شناورها | کاپیتان‌ها، افسران اول و راهنمایان شناورهای دریایی | کارشناسان عملیات فرودگاهی | کارشناسان لجستیک و زنجیره تأمین | مدیران ترابری، انبارداری و توزیع | مدیران ارشد اجرایی و عملیاتی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان آموزش و توسعه منابع انسانی | کارگران مواد منفجره، متخصصان جابه‌جایی مهمات و آتشبارها</t>
+          <t>مکانیک و تکنسین خدمات هواپیما | تکنسین‌های اویونیک و الکترونیک پرواز | مکانیک‌های ماشین‌آلات صنعتی | مکانیک تجهیزات سنگین متحرک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان | نصابان و تعمیرکاران تجهیزات رادیویی، سلولار و دکل‌های مخابراتی | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | اپراتورهای جرثقیل و تاورکرین | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | مهندسان فنی کشتی | ملوانان و روغن‌کاران شناورهای دریایی | کاپیتان‌ها، افسران اول و راهنمایان شناورهای دریایی | کارشناسان عملیات فرودگاهی | کارشناسان لجستیک و مدیریت زنجیره تأمین | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران کل و مدیران عملیات | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان مواد منفجره و آتش‌باری</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | جغرافیا | حمل‌ونقل | مکانیک | مدیریت و امور اداری | مخابرات | زبان انگلیسی | مهندسی و فناوری | پرسنلی و منابع انسانی | آموزش و تدریس</t>
+          <t>ایمنی و امنیت عمومی | جغرافیا | حمل و نقل | مکانیک | مدیریت و اداره | مخابرات | زبان انگلیسی | مهندسی و فناوری | پرسنل و منابع انسانی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | وضوح گفتار | تشخیص گفتار | دید نزدیک | دید دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | ابتکار | تقسیم زمان | تجسم فضایی | جهت‌یابی فضایی | زمان واکنش | ادراک عمق | توجه شنیداری</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | تقسیم توجه | تجسم | جهت‌گیری فضایی | زمان عکس‌العمل | درک عمق | توجه شنیداری</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>افسران گشت پلیس و کلانتری | سرپرستان رده‌اول مأموران پلیس و کارآگاهان | کارآگاهان و بازرسان پرونده‌های جنایی | آتش‌نشانان | سرپرستان رده‌اول کارکنان آتش‌نشانی و پیشگیری از حریق | نگهبانان و مأموران حراست | افسران و مأموران مراقبت در زندان‌ها و ندامتگاه‌ها | مدیران مدیریت بحران و شرایط اضطراری | بازرسان گیت‌های امنیتی حمل‌ونقل | تکنسین‌های فوریت‌های پزشکی (اورژانس) | مدیران ارشد اجرایی و عملیاتی | کارشناسان لجستیک و زنجیره تأمین | مدیران ترابری، انبارداری و توزیع | مدیران عامل | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان انطباق با مقررات و بازرسی | تکنسین‌های نقشه‌برداری و کاداستر | کارگران مواد منفجره، متخصصان جابه‌جایی مهمات و آتشبارها | کارگران تخصصی جمع‌آوری و امحای پسماندهای خطرناک</t>
+          <t>ماموران گشت پلیس و کلانتری | سرپرستان رده‌اول پلیس و کارآگاهان | کارآگاهان و بازرسان جنایی | آتش‌نشانان | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | نگهبانان و ماموران حراست | مأموران زندان و بازداشتگاه | مدیران مدیریت بحران و پدافند غیرعامل | ماموران بازرسی و کنترل امنیتی حمل‌ونقل | تکنسین‌های فوریت‌های پزشکی | مدیران کل و مدیران عملیات | کارشناسان لجستیک و مدیریت زنجیره تأمین | مدیران حمل‌ونقل، انبارداری و توزیع | مدیران عامل و مدیران ارشد اجرایی | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان پایش انطباق و بازرسی مقرراتی | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | کارشناسان مواد منفجره و آتش‌باری | کارگران امحا و پاک‌سازی مواد خطرناک</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
